--- a/artfynd/S 1000-2026 artfynd.xlsx
+++ b/artfynd/S 1000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,27 +4167,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134401414</v>
+        <v>137157068</v>
       </c>
       <c r="B29" t="n">
-        <v>56706</v>
+        <v>9417</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206046</v>
+        <v>101246</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4200,35 +4200,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Verkö, Verkö, Bl</t>
+          <t>Mjölkbergaviken, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540401</v>
+        <v>540604</v>
       </c>
       <c r="R29" t="n">
-        <v>6224793</v>
+        <v>6225377</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4252,22 +4236,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hane utan bakkropp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4282,44 +4271,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Oskarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Oskarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134401414</t>
+          <t>https://artportalen.se/Sighting/137157068</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111456940</v>
+        <v>134401414</v>
       </c>
       <c r="B30" t="n">
-        <v>58826</v>
+        <v>56706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>208242</v>
+        <v>206046</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4329,10 +4318,9 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>adult</t>
@@ -4341,7 +4329,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4351,17 +4339,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Näsmarkens våtmark, Verkö, Bl</t>
+          <t>Verkö, Verkö, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540405</v>
+        <v>540401</v>
       </c>
       <c r="R30" t="n">
-        <v>6224977</v>
+        <v>6224793</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4385,17 +4373,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>För att studera hur många som fanns på detta ställe så använde jag en hov och lade de i en genomskinlig plastbunke för att studera, räkna dem och se hur deras kondition var. Jag fick de till 10 honor och 5 hanar. Sedan släppte jag självklart tillbaka de på samma ställe igen.</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4404,7 +4397,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4422,13 +4414,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111456940</t>
+          <t>https://artportalen.se/Sighting/134401414</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112201777</v>
+        <v>111456940</v>
       </c>
       <c r="B31" t="n">
         <v>58826</v>
@@ -4458,19 +4450,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4484,10 +4476,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540404</v>
+        <v>540405</v>
       </c>
       <c r="R31" t="n">
-        <v>6224973</v>
+        <v>6224977</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4514,22 +4506,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2020-04-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2020-04-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>För att studera hur många som fanns på detta ställe så använde jag en hov och lade de i en genomskinlig plastbunke för att studera, räkna dem och se hur deras kondition var. Jag fick de till 10 honor och 5 hanar. Sedan släppte jag självklart tillbaka de på samma ställe igen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4556,13 +4543,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112201777</t>
+          <t>https://artportalen.se/Sighting/111456940</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124951111</v>
+        <v>112201777</v>
       </c>
       <c r="B32" t="n">
         <v>58826</v>
@@ -4592,15 +4579,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4617,10 +4608,10 @@
         <v>540404</v>
       </c>
       <c r="R32" t="n">
-        <v>6224979</v>
+        <v>6224973</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4644,22 +4635,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4686,13 +4677,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124951111</t>
+          <t>https://artportalen.se/Sighting/112201777</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125438214</v>
+        <v>124951111</v>
       </c>
       <c r="B33" t="n">
         <v>58826</v>
@@ -4722,20 +4713,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>parning/parningsceremonier</t>
@@ -4752,13 +4735,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540406</v>
+        <v>540404</v>
       </c>
       <c r="R33" t="n">
-        <v>6224983</v>
+        <v>6224979</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4782,27 +4765,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Jag räknade till 12 individer sammanlagt och 6 stycken av dem simmade i vattnet efter föda.</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4829,16 +4807,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125438214</t>
+          <t>https://artportalen.se/Sighting/124951111</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111437962</v>
+        <v>125438214</v>
       </c>
       <c r="B34" t="n">
-        <v>56876</v>
+        <v>58826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4846,26 +4824,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208257</v>
+        <v>208242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4874,10 +4852,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4887,17 +4869,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stigen vid våtmarken, Verkö, Bl</t>
+          <t>Näsmarkens våtmark, Verkö, Bl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540414</v>
+        <v>540406</v>
       </c>
       <c r="R34" t="n">
-        <v>6224753</v>
+        <v>6224983</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4921,17 +4903,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Låg och solade på stigen.</t>
+          <t>Jag räknade till 12 individer sammanlagt och 6 stycken av dem simmade i vattnet efter föda.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4958,13 +4950,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111437962</t>
+          <t>https://artportalen.se/Sighting/125438214</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112201861</v>
+        <v>111437962</v>
       </c>
       <c r="B35" t="n">
         <v>56876</v>
@@ -5016,17 +5008,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kopparödlan låg vid en rutten bokstubbe på Näsmarken (kolla kartan), Verkö, Bl</t>
+          <t>Stigen vid våtmarken, Verkö, Bl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540753</v>
+        <v>540414</v>
       </c>
       <c r="R35" t="n">
-        <v>6225084</v>
+        <v>6224753</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5050,27 +5042,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Den låg vid en rutten bokstubbe på Näsmarken.</t>
+          <t>Låg och solade på stigen.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5097,38 +5079,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112201861</t>
+          <t>https://artportalen.se/Sighting/111437962</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>83575175</v>
+        <v>112201861</v>
       </c>
       <c r="B36" t="n">
-        <v>106813</v>
+        <v>56876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220785</v>
+        <v>208257</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5136,16 +5118,33 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Kopparödlan låg vid en rutten bokstubbe på Näsmarken (kolla kartan), Verkö, Bl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540658</v>
+        <v>540753</v>
       </c>
       <c r="R36" t="n">
-        <v>6225366</v>
+        <v>6225084</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5170,19 +5169,29 @@
           <t>Lösen</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2DABF943-7A54-40FF-BB43-9277D5F1BBEF</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2008-02-13</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2008-02-13</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Den låg vid en rutten bokstubbe på Näsmarken.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5191,34 +5200,31 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Daniel Oskarsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Annika Lydänge</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Daniel Oskarsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83575175</t>
+          <t>https://artportalen.se/Sighting/112201861</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>83575456</v>
+        <v>83575175</v>
       </c>
       <c r="B37" t="n">
         <v>106813</v>
@@ -5257,10 +5263,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540708</v>
+        <v>540658</v>
       </c>
       <c r="R37" t="n">
-        <v>6225012</v>
+        <v>6225366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5287,17 +5293,17 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>0D21071A-D93F-4177-A223-42C988595C99</t>
+          <t>2DABF943-7A54-40FF-BB43-9277D5F1BBEF</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2008-02-14</t>
+          <t>2008-02-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2008-02-14</t>
+          <t>2008-02-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5327,13 +5333,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83575456</t>
+          <t>https://artportalen.se/Sighting/83575175</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>83576712</v>
+        <v>83575456</v>
       </c>
       <c r="B38" t="n">
         <v>106813</v>
@@ -5372,10 +5378,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540461</v>
+        <v>540708</v>
       </c>
       <c r="R38" t="n">
-        <v>6224943</v>
+        <v>6225012</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5402,17 +5408,17 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>F1AF2AA6-BEB6-42EE-AAA2-4D5470F2810D</t>
+          <t>0D21071A-D93F-4177-A223-42C988595C99</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2008-02-19</t>
+          <t>2008-02-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2008-02-19</t>
+          <t>2008-02-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5442,13 +5448,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83576712</t>
+          <t>https://artportalen.se/Sighting/83575456</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>83576786</v>
+        <v>83576712</v>
       </c>
       <c r="B39" t="n">
         <v>106813</v>
@@ -5487,10 +5493,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540487</v>
+        <v>540461</v>
       </c>
       <c r="R39" t="n">
-        <v>6225046</v>
+        <v>6224943</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5517,7 +5523,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>AD60FDE1-37C7-42E9-85E0-96AD2B3D89C3</t>
+          <t>F1AF2AA6-BEB6-42EE-AAA2-4D5470F2810D</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5557,13 +5563,13 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83576786</t>
+          <t>https://artportalen.se/Sighting/83576712</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>83577225</v>
+        <v>83576786</v>
       </c>
       <c r="B40" t="n">
         <v>106813</v>
@@ -5602,10 +5608,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540478</v>
+        <v>540487</v>
       </c>
       <c r="R40" t="n">
-        <v>6224859</v>
+        <v>6225046</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5632,7 +5638,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>79638DEF-6EB8-493E-AA7A-CB2A06AC291D</t>
+          <t>AD60FDE1-37C7-42E9-85E0-96AD2B3D89C3</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5672,13 +5678,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83577225</t>
+          <t>https://artportalen.se/Sighting/83576786</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>83605368</v>
+        <v>83577225</v>
       </c>
       <c r="B41" t="n">
         <v>106813</v>
@@ -5717,10 +5723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540472</v>
+        <v>540478</v>
       </c>
       <c r="R41" t="n">
-        <v>6224885</v>
+        <v>6224859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5747,7 +5753,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>8F4831BE-4FEB-4DCC-A86B-8706DA474603</t>
+          <t>79638DEF-6EB8-493E-AA7A-CB2A06AC291D</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5786,6 +5792,121 @@
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83577225</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>83605368</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>540472</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6224885</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>8F4831BE-4FEB-4DCC-A86B-8706DA474603</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2008-02-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2008-02-19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83605368</t>
         </is>
@@ -5833,6 +5954,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1000-2026 artfynd.xlsx
+++ b/artfynd/S 1000-2026 artfynd.xlsx
@@ -4170,7 +4170,7 @@
         <v>137157068</v>
       </c>
       <c r="B29" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 1000-2026 artfynd.xlsx
+++ b/artfynd/S 1000-2026 artfynd.xlsx
@@ -4170,7 +4170,7 @@
         <v>137157068</v>
       </c>
       <c r="B29" t="n">
-        <v>9418</v>
+        <v>9424</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 1000-2026 artfynd.xlsx
+++ b/artfynd/S 1000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4288,27 +4288,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134401414</v>
+        <v>137341537</v>
       </c>
       <c r="B30" t="n">
-        <v>56706</v>
+        <v>9424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206046</v>
+        <v>101246</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4321,35 +4321,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Verkö, Verkö, Bl</t>
+          <t>Näsmarken, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540401</v>
+        <v>540538</v>
       </c>
       <c r="R30" t="n">
-        <v>6224793</v>
+        <v>6225256</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4373,22 +4362,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hane utan bakkropp, men rörde sig fortfarande.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4403,44 +4397,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Oskarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Oskarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134401414</t>
+          <t>https://artportalen.se/Sighting/137341537</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111456940</v>
+        <v>134401414</v>
       </c>
       <c r="B31" t="n">
-        <v>58826</v>
+        <v>56706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208242</v>
+        <v>206046</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4450,10 +4444,9 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>adult</t>
@@ -4462,7 +4455,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4472,17 +4465,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Näsmarkens våtmark, Verkö, Bl</t>
+          <t>Verkö, Verkö, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540405</v>
+        <v>540401</v>
       </c>
       <c r="R31" t="n">
-        <v>6224977</v>
+        <v>6224793</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4506,17 +4499,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>För att studera hur många som fanns på detta ställe så använde jag en hov och lade de i en genomskinlig plastbunke för att studera, räkna dem och se hur deras kondition var. Jag fick de till 10 honor och 5 hanar. Sedan släppte jag självklart tillbaka de på samma ställe igen.</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4525,7 +4523,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4543,13 +4540,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111456940</t>
+          <t>https://artportalen.se/Sighting/134401414</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112201777</v>
+        <v>111456940</v>
       </c>
       <c r="B32" t="n">
         <v>58826</v>
@@ -4579,19 +4576,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4605,10 +4602,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540404</v>
+        <v>540405</v>
       </c>
       <c r="R32" t="n">
-        <v>6224973</v>
+        <v>6224977</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4635,22 +4632,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2020-04-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2020-04-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>För att studera hur många som fanns på detta ställe så använde jag en hov och lade de i en genomskinlig plastbunke för att studera, räkna dem och se hur deras kondition var. Jag fick de till 10 honor och 5 hanar. Sedan släppte jag självklart tillbaka de på samma ställe igen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4677,13 +4669,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112201777</t>
+          <t>https://artportalen.se/Sighting/111456940</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124951111</v>
+        <v>112201777</v>
       </c>
       <c r="B33" t="n">
         <v>58826</v>
@@ -4713,15 +4705,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4738,10 +4734,10 @@
         <v>540404</v>
       </c>
       <c r="R33" t="n">
-        <v>6224979</v>
+        <v>6224973</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4765,22 +4761,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4807,13 +4803,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124951111</t>
+          <t>https://artportalen.se/Sighting/112201777</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125438214</v>
+        <v>124951111</v>
       </c>
       <c r="B34" t="n">
         <v>58826</v>
@@ -4843,20 +4839,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>parning/parningsceremonier</t>
@@ -4873,13 +4861,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540406</v>
+        <v>540404</v>
       </c>
       <c r="R34" t="n">
-        <v>6224983</v>
+        <v>6224979</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4903,27 +4891,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Jag räknade till 12 individer sammanlagt och 6 stycken av dem simmade i vattnet efter föda.</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4950,16 +4933,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125438214</t>
+          <t>https://artportalen.se/Sighting/124951111</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111437962</v>
+        <v>125438214</v>
       </c>
       <c r="B35" t="n">
-        <v>56876</v>
+        <v>58826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4967,26 +4950,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208257</v>
+        <v>208242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4995,10 +4978,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5008,17 +4995,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stigen vid våtmarken, Verkö, Bl</t>
+          <t>Näsmarkens våtmark, Verkö, Bl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540414</v>
+        <v>540406</v>
       </c>
       <c r="R35" t="n">
-        <v>6224753</v>
+        <v>6224983</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5042,17 +5029,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Låg och solade på stigen.</t>
+          <t>Jag räknade till 12 individer sammanlagt och 6 stycken av dem simmade i vattnet efter föda.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5079,13 +5076,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111437962</t>
+          <t>https://artportalen.se/Sighting/125438214</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112201861</v>
+        <v>111437962</v>
       </c>
       <c r="B36" t="n">
         <v>56876</v>
@@ -5137,17 +5134,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kopparödlan låg vid en rutten bokstubbe på Näsmarken (kolla kartan), Verkö, Bl</t>
+          <t>Stigen vid våtmarken, Verkö, Bl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540753</v>
+        <v>540414</v>
       </c>
       <c r="R36" t="n">
-        <v>6225084</v>
+        <v>6224753</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5171,27 +5168,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Den låg vid en rutten bokstubbe på Näsmarken.</t>
+          <t>Låg och solade på stigen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5218,38 +5205,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112201861</t>
+          <t>https://artportalen.se/Sighting/111437962</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>83575175</v>
+        <v>112201861</v>
       </c>
       <c r="B37" t="n">
-        <v>106813</v>
+        <v>56876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>208257</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5257,16 +5244,33 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Kopparödlan låg vid en rutten bokstubbe på Näsmarken (kolla kartan), Verkö, Bl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540658</v>
+        <v>540753</v>
       </c>
       <c r="R37" t="n">
-        <v>6225366</v>
+        <v>6225084</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5291,19 +5295,29 @@
           <t>Lösen</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2DABF943-7A54-40FF-BB43-9277D5F1BBEF</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2008-02-13</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2008-02-13</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Den låg vid en rutten bokstubbe på Näsmarken.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5312,34 +5326,31 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Daniel Oskarsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Annika Lydänge</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Daniel Oskarsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83575175</t>
+          <t>https://artportalen.se/Sighting/112201861</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>83575456</v>
+        <v>83575175</v>
       </c>
       <c r="B38" t="n">
         <v>106813</v>
@@ -5378,10 +5389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540708</v>
+        <v>540658</v>
       </c>
       <c r="R38" t="n">
-        <v>6225012</v>
+        <v>6225366</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5408,17 +5419,17 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0D21071A-D93F-4177-A223-42C988595C99</t>
+          <t>2DABF943-7A54-40FF-BB43-9277D5F1BBEF</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2008-02-14</t>
+          <t>2008-02-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2008-02-14</t>
+          <t>2008-02-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5448,13 +5459,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83575456</t>
+          <t>https://artportalen.se/Sighting/83575175</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>83576712</v>
+        <v>83575456</v>
       </c>
       <c r="B39" t="n">
         <v>106813</v>
@@ -5493,10 +5504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540461</v>
+        <v>540708</v>
       </c>
       <c r="R39" t="n">
-        <v>6224943</v>
+        <v>6225012</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5523,17 +5534,17 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>F1AF2AA6-BEB6-42EE-AAA2-4D5470F2810D</t>
+          <t>0D21071A-D93F-4177-A223-42C988595C99</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2008-02-19</t>
+          <t>2008-02-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2008-02-19</t>
+          <t>2008-02-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5563,13 +5574,13 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83576712</t>
+          <t>https://artportalen.se/Sighting/83575456</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>83576786</v>
+        <v>83576712</v>
       </c>
       <c r="B40" t="n">
         <v>106813</v>
@@ -5608,10 +5619,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540487</v>
+        <v>540461</v>
       </c>
       <c r="R40" t="n">
-        <v>6225046</v>
+        <v>6224943</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5638,7 +5649,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>AD60FDE1-37C7-42E9-85E0-96AD2B3D89C3</t>
+          <t>F1AF2AA6-BEB6-42EE-AAA2-4D5470F2810D</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5678,13 +5689,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83576786</t>
+          <t>https://artportalen.se/Sighting/83576712</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>83577225</v>
+        <v>83576786</v>
       </c>
       <c r="B41" t="n">
         <v>106813</v>
@@ -5723,10 +5734,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540478</v>
+        <v>540487</v>
       </c>
       <c r="R41" t="n">
-        <v>6224859</v>
+        <v>6225046</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5753,7 +5764,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>79638DEF-6EB8-493E-AA7A-CB2A06AC291D</t>
+          <t>AD60FDE1-37C7-42E9-85E0-96AD2B3D89C3</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5793,13 +5804,13 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83577225</t>
+          <t>https://artportalen.se/Sighting/83576786</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>83605368</v>
+        <v>83577225</v>
       </c>
       <c r="B42" t="n">
         <v>106813</v>
@@ -5838,10 +5849,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540472</v>
+        <v>540478</v>
       </c>
       <c r="R42" t="n">
-        <v>6224885</v>
+        <v>6224859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5868,7 +5879,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>8F4831BE-4FEB-4DCC-A86B-8706DA474603</t>
+          <t>79638DEF-6EB8-493E-AA7A-CB2A06AC291D</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5907,6 +5918,121 @@
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83577225</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>83605368</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>540472</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6224885</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>8F4831BE-4FEB-4DCC-A86B-8706DA474603</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2008-02-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2008-02-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83605368</t>
         </is>
@@ -5955,6 +6081,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
